--- a/artfynd/A 47348-2025 artfynd.xlsx
+++ b/artfynd/A 47348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129281655</v>
       </c>
       <c r="B2" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129281664</v>
       </c>
       <c r="B3" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129281657</v>
       </c>
       <c r="B4" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129281656</v>
       </c>
       <c r="B5" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129281658</v>
       </c>
       <c r="B6" t="n">
-        <v>105732</v>
+        <v>105739</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129281659</v>
       </c>
       <c r="B7" t="n">
-        <v>107376</v>
+        <v>107383</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129281668</v>
       </c>
       <c r="B8" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47348-2025 artfynd.xlsx
+++ b/artfynd/A 47348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129281655</v>
       </c>
       <c r="B2" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129281664</v>
       </c>
       <c r="B3" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129281657</v>
       </c>
       <c r="B4" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129281656</v>
       </c>
       <c r="B5" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129281658</v>
       </c>
       <c r="B6" t="n">
-        <v>105739</v>
+        <v>105741</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129281659</v>
       </c>
       <c r="B7" t="n">
-        <v>107383</v>
+        <v>107385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129281668</v>
       </c>
       <c r="B8" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47348-2025 artfynd.xlsx
+++ b/artfynd/A 47348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129281655</v>
       </c>
       <c r="B2" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129281664</v>
       </c>
       <c r="B3" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129281657</v>
       </c>
       <c r="B4" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129281656</v>
       </c>
       <c r="B5" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129281658</v>
       </c>
       <c r="B6" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129281659</v>
       </c>
       <c r="B7" t="n">
-        <v>107385</v>
+        <v>107411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129281668</v>
       </c>
       <c r="B8" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47348-2025 artfynd.xlsx
+++ b/artfynd/A 47348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129281655</v>
       </c>
       <c r="B2" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129281664</v>
       </c>
       <c r="B3" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129281657</v>
       </c>
       <c r="B4" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129281656</v>
       </c>
       <c r="B5" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129281658</v>
       </c>
       <c r="B6" t="n">
-        <v>105767</v>
+        <v>105769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129281659</v>
       </c>
       <c r="B7" t="n">
-        <v>107411</v>
+        <v>107413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129281668</v>
       </c>
       <c r="B8" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47348-2025 artfynd.xlsx
+++ b/artfynd/A 47348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129281655</v>
       </c>
       <c r="B2" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129281657</v>
       </c>
       <c r="B4" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129281656</v>
       </c>
       <c r="B5" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129281658</v>
       </c>
       <c r="B6" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129281659</v>
       </c>
       <c r="B7" t="n">
-        <v>107413</v>
+        <v>107414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129281668</v>
       </c>
       <c r="B8" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47348-2025 artfynd.xlsx
+++ b/artfynd/A 47348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129281655</v>
       </c>
       <c r="B2" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129281664</v>
       </c>
       <c r="B3" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129281657</v>
       </c>
       <c r="B4" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129281656</v>
       </c>
       <c r="B5" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129281658</v>
       </c>
       <c r="B6" t="n">
-        <v>105770</v>
+        <v>105774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129281659</v>
       </c>
       <c r="B7" t="n">
-        <v>107414</v>
+        <v>107418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129281668</v>
       </c>
       <c r="B8" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47348-2025 artfynd.xlsx
+++ b/artfynd/A 47348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129281655</v>
       </c>
       <c r="B2" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129281664</v>
       </c>
       <c r="B3" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129281657</v>
       </c>
       <c r="B4" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129281656</v>
       </c>
       <c r="B5" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129281658</v>
       </c>
       <c r="B6" t="n">
-        <v>105774</v>
+        <v>105776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129281659</v>
       </c>
       <c r="B7" t="n">
-        <v>107418</v>
+        <v>107420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129281668</v>
       </c>
       <c r="B8" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47348-2025 artfynd.xlsx
+++ b/artfynd/A 47348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129281655</v>
       </c>
       <c r="B2" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129281664</v>
       </c>
       <c r="B3" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129281657</v>
       </c>
       <c r="B4" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129281656</v>
       </c>
       <c r="B5" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129281658</v>
       </c>
       <c r="B6" t="n">
-        <v>105776</v>
+        <v>105780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129281659</v>
       </c>
       <c r="B7" t="n">
-        <v>107420</v>
+        <v>107424</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129281668</v>
       </c>
       <c r="B8" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47348-2025 artfynd.xlsx
+++ b/artfynd/A 47348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129281655</v>
       </c>
       <c r="B2" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129281664</v>
       </c>
       <c r="B3" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129281657</v>
       </c>
       <c r="B4" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129281656</v>
       </c>
       <c r="B5" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129281658</v>
       </c>
       <c r="B6" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129281659</v>
       </c>
       <c r="B7" t="n">
-        <v>107424</v>
+        <v>107434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129281668</v>
       </c>
       <c r="B8" t="n">
-        <v>96312</v>
+        <v>96320</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47348-2025 artfynd.xlsx
+++ b/artfynd/A 47348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129281655</v>
       </c>
       <c r="B2" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129281664</v>
       </c>
       <c r="B3" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129281657</v>
       </c>
       <c r="B4" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129281656</v>
       </c>
       <c r="B5" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129281658</v>
       </c>
       <c r="B6" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129281659</v>
       </c>
       <c r="B7" t="n">
-        <v>107434</v>
+        <v>107437</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129281668</v>
       </c>
       <c r="B8" t="n">
-        <v>96320</v>
+        <v>96323</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47348-2025 artfynd.xlsx
+++ b/artfynd/A 47348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129281655</v>
       </c>
       <c r="B2" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129281664</v>
       </c>
       <c r="B3" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129281657</v>
       </c>
       <c r="B4" t="n">
-        <v>105793</v>
+        <v>105822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129281656</v>
       </c>
       <c r="B5" t="n">
-        <v>105793</v>
+        <v>105822</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129281658</v>
       </c>
       <c r="B6" t="n">
-        <v>105793</v>
+        <v>105822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129281659</v>
       </c>
       <c r="B7" t="n">
-        <v>107437</v>
+        <v>107466</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129281668</v>
       </c>
       <c r="B8" t="n">
-        <v>96323</v>
+        <v>96352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47348-2025 artfynd.xlsx
+++ b/artfynd/A 47348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129281655</v>
       </c>
       <c r="B2" t="n">
-        <v>100945</v>
+        <v>100957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129281664</v>
       </c>
       <c r="B3" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129281657</v>
       </c>
       <c r="B4" t="n">
-        <v>105822</v>
+        <v>105834</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129281656</v>
       </c>
       <c r="B5" t="n">
-        <v>105822</v>
+        <v>105834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129281658</v>
       </c>
       <c r="B6" t="n">
-        <v>105822</v>
+        <v>105834</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129281659</v>
       </c>
       <c r="B7" t="n">
-        <v>107466</v>
+        <v>107478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129281668</v>
       </c>
       <c r="B8" t="n">
-        <v>96352</v>
+        <v>96364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47348-2025 artfynd.xlsx
+++ b/artfynd/A 47348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129281655</v>
       </c>
       <c r="B2" t="n">
-        <v>100957</v>
+        <v>100958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129281664</v>
       </c>
       <c r="B3" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>129281657</v>
       </c>
       <c r="B4" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>129281656</v>
       </c>
       <c r="B5" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>129281658</v>
       </c>
       <c r="B6" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>129281659</v>
       </c>
       <c r="B7" t="n">
-        <v>107478</v>
+        <v>107479</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>129281668</v>
       </c>
       <c r="B8" t="n">
-        <v>96364</v>
+        <v>96365</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 47348-2025 artfynd.xlsx
+++ b/artfynd/A 47348-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281668</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281664</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281652</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281659</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281656</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281657</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281658</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1471,8 +1511,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129281655</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>